--- a/results/Int Task Remove ACC 0.3/Rando_fi_explain.xlsx
+++ b/results/Int Task Remove ACC 0.3/Rando_fi_explain.xlsx
@@ -1148,268 +1148,268 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0005721557830199398</v>
+        <v>0.0009769030901449313</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.003983725630250125</v>
+        <v>-0.002597214056072721</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000808914836540496</v>
+        <v>-0.0002227964329208065</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.001908306475131811</v>
+        <v>0.0007194959950488833</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0007731245653704487</v>
+        <v>-0.0001346528764655808</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003499283407559636</v>
+        <v>0.002083082739460802</v>
       </c>
       <c r="I3" t="n">
-        <v>2.803877042056425e-05</v>
+        <v>6.176031052259169e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0008820595100932652</v>
+        <v>0.001680264958028819</v>
       </c>
       <c r="K3" t="n">
-        <v>0.009365613794465679</v>
+        <v>0.0109959504756746</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008222602961103087</v>
+        <v>0.01119419259244329</v>
       </c>
       <c r="M3" t="n">
-        <v>5.700235811762597e-05</v>
+        <v>0.0007188485038131066</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.002468687314760864</v>
+        <v>-0.001559643080278968</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0009478335039645625</v>
+        <v>0.003707709339257231</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01290607963858181</v>
+        <v>0.0165273788745781</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.007662295589419413</v>
+        <v>0.004772867386552266</v>
       </c>
       <c r="R3" t="n">
-        <v>0.002337185626136095</v>
+        <v>0.001869020169000995</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0007369948367238067</v>
+        <v>-0.001378099369459374</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.002348553245732392</v>
+        <v>-0.001269112867445567</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0003901165509183989</v>
+        <v>0.001151993831918198</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0001048139764741995</v>
+        <v>7.014640860144692e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>0.00341347020302515</v>
+        <v>0.007878884406415753</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0002931878589779479</v>
+        <v>-0.0002557330253315148</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.000167682591705317</v>
+        <v>0.0008845031799529788</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.0002946565929708255</v>
+        <v>0.0005647354893560297</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0009122608525908181</v>
+        <v>0.0005352122556439743</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0001736304797999677</v>
+        <v>0.0002688512065309234</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.002846691292922206</v>
+        <v>-0.002331253029475196</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.004790243541355099</v>
+        <v>-0.000832564608971793</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.0003319637191227242</v>
+        <v>0.002653769208101545</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.002849443731501866</v>
+        <v>0.002521822571353261</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.000105621865132568</v>
+        <v>0.0002046353894011754</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.0001342431986523385</v>
+        <v>9.1896256127333e-06</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.001057302051863862</v>
+        <v>0.001110674275675844</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.002666364072898449</v>
+        <v>0.0009715796655024988</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.0003782890708209441</v>
+        <v>9.387650172955063e-05</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.0003584634123433284</v>
+        <v>0.0005307509719112769</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.0001238394129226529</v>
+        <v>-0.001767063537995847</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.0001049325500302868</v>
+        <v>0.001944900040827517</v>
       </c>
       <c r="AP3" t="n">
-        <v>-7.361214234510968e-05</v>
+        <v>0.0001608433217835559</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.0006117619636770311</v>
+        <v>0.001749766231436783</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.001339097399688113</v>
+        <v>0.002544532871609187</v>
       </c>
       <c r="AS3" t="n">
-        <v>-0.0002455129629492303</v>
+        <v>-8.36070850596038e-05</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.0051679293074056</v>
+        <v>0.001926979636468538</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.0004535123078765602</v>
+        <v>0.0001351907451551559</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.001203040232581896</v>
+        <v>0.002585180340132652</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.0006174423430672927</v>
+        <v>0.001260735783171198</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.0003943800365324113</v>
+        <v>0.0007021522262786916</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.0003124111678844068</v>
+        <v>-3.648700827649787e-05</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.0004665969324970996</v>
+        <v>0.003215836353623619</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0.007024553993373911</v>
+        <v>-0.001589557364013866</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0.007994930977577638</v>
+        <v>-0.002996161444979582</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.000429603437339171</v>
+        <v>0.0003329070999582596</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.0002772123924319214</v>
+        <v>0.000152994399040921</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.0002829241500473167</v>
+        <v>-1.029327907611012e-05</v>
       </c>
       <c r="BF3" t="n">
-        <v>-0.003532942844384256</v>
+        <v>-0.003844714690907888</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.002467401103174194</v>
+        <v>0.001598229558598812</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>-0.0003387492065451769</v>
+        <v>0.0002647684325710009</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-0.001595474731070783</v>
+        <v>0.00260808158731476</v>
       </c>
       <c r="BK3" t="n">
-        <v>-2.086556532453487e-05</v>
+        <v>0.0006281006866500217</v>
       </c>
       <c r="BL3" t="n">
-        <v>-0.0001050031134200913</v>
+        <v>0.0001181156186899201</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.001083125912553804</v>
+        <v>0.002010581096781276</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0.009317907882214864</v>
+        <v>-0.00157919414292453</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0.002152200635206331</v>
+        <v>0.0009434641353447671</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.0003988767863906973</v>
+        <v>0.002686469415073516</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.0001518097907171301</v>
+        <v>0.000151431776018881</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.00166029478317668</v>
+        <v>0.003342397668438375</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.0006045476619656077</v>
+        <v>0.0006684987454666326</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.0001985783365660909</v>
+        <v>0.001764005846149208</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.002320609063425332</v>
+        <v>0.006351843003900274</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.0008700354623687701</v>
+        <v>0.002061927779678588</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.004549045980182539</v>
+        <v>0.006412215483154023</v>
       </c>
       <c r="BX3" t="n">
-        <v>-7.276766981536899e-05</v>
+        <v>3.026972570985718e-05</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.0003998992438985538</v>
+        <v>0.0006150132958721522</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-7.962382743987421e-05</v>
+        <v>0.0007511636735198301</v>
       </c>
       <c r="CA3" t="n">
         <v>0</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.0009023419841120862</v>
+        <v>0.0004347523212358529</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.0004292378251980666</v>
+        <v>0.002822363106889451</v>
       </c>
       <c r="CD3" t="n">
-        <v>3.694721378204146e-05</v>
+        <v>-0.0001009180024472845</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.0004536313234777523</v>
+        <v>0.0009976195196655948</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.001178215370228761</v>
+        <v>0.002619664891062322</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.0008762386577990221</v>
+        <v>-0.0003458627394410874</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.0001833632724060142</v>
+        <v>0.0007310046353071175</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.0009840124253683612</v>
+        <v>0.0004543026763297053</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.00421292278555818</v>
+        <v>0.005300067406724228</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.001767722791861196</v>
+        <v>0.000914993482541562</v>
       </c>
     </row>
     <row r="4">
@@ -1419,268 +1419,268 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002245700703729712</v>
+        <v>0.006449472398520426</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0146154923522392</v>
+        <v>0.01973246013173252</v>
       </c>
       <c r="E4" t="n">
-        <v>0.007122931352019771</v>
+        <v>0.005548040095268135</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004232431331336823</v>
+        <v>0.002528890489108567</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004653234076944557</v>
+        <v>0.008440849862877698</v>
       </c>
       <c r="H4" t="n">
-        <v>0.007836444205763791</v>
+        <v>0.005281222284859698</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0004635598129684617</v>
+        <v>0.0004176604008445587</v>
       </c>
       <c r="J4" t="n">
-        <v>0.008003337997713265</v>
+        <v>0.004988042525424599</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0269756220608364</v>
+        <v>0.02387399308558088</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0326103127127155</v>
+        <v>0.02369312409816193</v>
       </c>
       <c r="M4" t="n">
-        <v>0.002500866338750717</v>
+        <v>0.004569629597375435</v>
       </c>
       <c r="N4" t="n">
-        <v>0.009331179034768673</v>
+        <v>0.006747799611066298</v>
       </c>
       <c r="O4" t="n">
-        <v>0.005271271018762595</v>
+        <v>0.008681935756487413</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0201009725656967</v>
+        <v>0.01863082523696868</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01066693153104802</v>
+        <v>0.007759960441205177</v>
       </c>
       <c r="R4" t="n">
-        <v>0.00601061501036176</v>
+        <v>0.005951045201808947</v>
       </c>
       <c r="S4" t="n">
-        <v>0.005508745996252472</v>
+        <v>0.005731377369461846</v>
       </c>
       <c r="T4" t="n">
-        <v>0.007173660293673856</v>
+        <v>0.008386016624539677</v>
       </c>
       <c r="U4" t="n">
-        <v>0.004846652353191034</v>
+        <v>0.007503986223070262</v>
       </c>
       <c r="V4" t="n">
-        <v>0.000205330928373604</v>
+        <v>0.000561135636951778</v>
       </c>
       <c r="W4" t="n">
-        <v>0.01401575418515097</v>
+        <v>0.01265270826990992</v>
       </c>
       <c r="X4" t="n">
-        <v>0.004993674556568113</v>
+        <v>0.005496617201660503</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.004426221211920441</v>
+        <v>0.00376292979710181</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.003168828392778856</v>
+        <v>0.004604784623105943</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.00489511394789686</v>
+        <v>0.004200509890422632</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0007219308695382656</v>
+        <v>0.0007616110486275062</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.01067549936125239</v>
+        <v>0.009055330747155163</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.004359568877205245</v>
+        <v>0.007548232521874575</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.005342498484055847</v>
+        <v>0.007803780821692656</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.007766624887877598</v>
+        <v>0.00839437479671209</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.000589618792252977</v>
+        <v>0.0006091418330449038</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.0009927827051745754</v>
+        <v>0.0009064320021387184</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.007179323862457916</v>
+        <v>0.008544859672220632</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.005564267454283345</v>
+        <v>0.005304166272631043</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.0007765624419940908</v>
+        <v>0.00103599296727802</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.0008327390572593502</v>
+        <v>0.0008855534750529563</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.004507625938126774</v>
+        <v>0.002580566127662708</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.003137600480767083</v>
+        <v>0.006474400923671351</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.001121580948635053</v>
+        <v>0.001649209609196055</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.005270847293225889</v>
+        <v>0.002821645835834673</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.004901681552230946</v>
+        <v>0.006088151078198775</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.002892447918183427</v>
+        <v>0.002838219827452274</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.014813837059431</v>
+        <v>0.01150732907901442</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.004879810099798881</v>
+        <v>0.005486897534753622</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.005353779996767769</v>
+        <v>0.002830808210962594</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.008564641168577428</v>
+        <v>0.008499337344808115</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.001022697796147112</v>
+        <v>0.0009851816840923259</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.008409392191620464</v>
+        <v>0.003346485542362899</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.007813778629742463</v>
+        <v>0.007328808946606123</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.01442614453836892</v>
+        <v>0.006126798929875185</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.008350738042273846</v>
+        <v>0.006531888824027452</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0009553087450008341</v>
+        <v>0.0007044474879444352</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.0008261186116335085</v>
+        <v>0.001055210685360185</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.001809757364042731</v>
+        <v>0.001438190456501773</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.009211341505077719</v>
+        <v>0.005695903826919116</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.01083971600528576</v>
+        <v>0.008570676837128212</v>
       </c>
       <c r="BH4" t="n">
         <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.001147231689234059</v>
+        <v>0.001357958113695844</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.00932294127516773</v>
+        <v>0.008657693797242903</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.01235621366489885</v>
+        <v>0.0080353323730252</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.001043787064006481</v>
+        <v>0.0009845876617210225</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.004559259394107272</v>
+        <v>0.006561972291579454</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.01436626942133713</v>
+        <v>0.009948812608785756</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.005763058298325196</v>
+        <v>0.005773181441061512</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.007511209481469781</v>
+        <v>0.006502484700509445</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.0005453632454759785</v>
+        <v>0.0005279216208761255</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.005423348376908672</v>
+        <v>0.006833074673674609</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.003658680743517524</v>
+        <v>0.003937602853574088</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.002008265436478844</v>
+        <v>0.00318450130822499</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.006991453922152184</v>
+        <v>0.009579244049012706</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.00642384608505361</v>
+        <v>0.004679763624851502</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.008518124859792715</v>
+        <v>0.006907351019294914</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.0002116657875076733</v>
+        <v>0.0004218688761852395</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.001434762980224069</v>
+        <v>0.001346982020518057</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.000958156465180913</v>
+        <v>0.00171219882091849</v>
       </c>
       <c r="CA4" t="n">
         <v>0</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.002762790906745857</v>
+        <v>0.001419045730269949</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.002274554175583867</v>
+        <v>0.005910533428343459</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.0001507881127825373</v>
+        <v>0.0003983493426012247</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.001311620441056875</v>
+        <v>0.001725750301566146</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.00418714577060283</v>
+        <v>0.003658048239887391</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.00436558123818561</v>
+        <v>0.004218330441252582</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.001830832188893269</v>
+        <v>0.001429616440408113</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.005284153135857264</v>
+        <v>0.004991215766018246</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.007861058804242304</v>
+        <v>0.009519248995998443</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.005526216090457446</v>
+        <v>0.005960145946517977</v>
       </c>
     </row>
     <row r="5">
@@ -1690,268 +1690,268 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.003414839797639136</v>
+        <v>-0.006216984965461214</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.03161316537992689</v>
+        <v>-0.0400707825403067</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.01710578057412502</v>
+        <v>-0.009630231613165407</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.01045531197301854</v>
+        <v>-0.002620456466610333</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.01015847216578628</v>
+        <v>-0.01950426655830965</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.01007074490220559</v>
+        <v>-0.008281315022888026</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0007028504490433907</v>
+        <v>-0.0005409904286308387</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.01131918435289222</v>
+        <v>-0.009488139825218433</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.03878583473861722</v>
+        <v>-0.01800168634064083</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.05113827993254637</v>
+        <v>-0.01713370696557244</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.004307192198293408</v>
+        <v>-0.004443554843875075</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.02255180820804554</v>
+        <v>-0.01116791191506094</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.00497470489038786</v>
+        <v>-0.008611875737318109</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.0197404640188753</v>
+        <v>-0.01502162799842701</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.01096877502001595</v>
+        <v>-0.006645316253002365</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.004369538077403268</v>
+        <v>-0.004993757802746535</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.007156901297679885</v>
+        <v>-0.01487200325071112</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.01306699958385353</v>
+        <v>-0.01925540432345875</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.00637952052011378</v>
+        <v>-0.006763664962642513</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.0002733307301835408</v>
+        <v>-0.0004325599685410686</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.02810248198558842</v>
+        <v>-0.01597277822257804</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.005464480874316935</v>
+        <v>-0.006200582605076954</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.007536118703631423</v>
+        <v>-0.003123779773525937</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.00882467786021086</v>
+        <v>-0.009878953533775835</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.006130417805544741</v>
+        <v>-0.00567465321563686</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.001366653650917649</v>
+        <v>-0.0007078254030671971</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.01950426655830968</v>
+        <v>-0.02133279154815119</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.01193778898696933</v>
+        <v>-0.007566052842273819</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.007440100882723844</v>
+        <v>-0.004570230607966486</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.006037735849056614</v>
+        <v>-0.01223470661672904</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.0007205764611689202</v>
+        <v>-0.0009155222638368321</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.002005505308690469</v>
+        <v>-0.001160928742994372</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.01193778898696931</v>
+        <v>-0.01331668747399082</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.009987410826689035</v>
+        <v>-0.00936329588014978</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.001132075471698124</v>
+        <v>-0.001327606403748494</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.001401120896717345</v>
+        <v>-0.0008739076154805958</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.008980866848887169</v>
+        <v>-0.005364291433146507</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.005086170659941158</v>
+        <v>-0.005444941080861476</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.001606086221470837</v>
+        <v>-0.001584721657862687</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.01023037875829755</v>
+        <v>-0.003423499577345768</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.004916700528240558</v>
+        <v>-0.004797483287455728</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.005733558178752107</v>
+        <v>-0.007354733848029271</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.04127318718381114</v>
+        <v>-0.01079258010118045</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.006450270495214327</v>
+        <v>-0.008553459119496898</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.003642914331465119</v>
+        <v>-0.001732882502113287</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.01801441152922335</v>
+        <v>-0.00984787830264211</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.001331668747399095</v>
+        <v>-0.0002535925612848877</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.01190178942987932</v>
+        <v>-0.006297548605240955</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.01083473861720068</v>
+        <v>-0.011665257819104</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.03794266441821247</v>
+        <v>-0.01530054644808747</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.02415682967959528</v>
+        <v>-0.00999156829679596</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.001789429879317517</v>
+        <v>-0.0009696458684654519</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.0006291781360597381</v>
+        <v>-0.001601281024819823</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.005112072355485608</v>
+        <v>-0.003127641589180086</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.01909357952161138</v>
+        <v>-0.01277021617293833</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.01547217537942666</v>
+        <v>-0.009190556492411484</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.002241793434747752</v>
+        <v>-0.002041633306645274</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.01429143314651716</v>
+        <v>-0.01023720349563042</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.02255480607082632</v>
+        <v>-0.0115723270440252</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.001563820794590043</v>
+        <v>-0.002108551347129994</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.00768614891913526</v>
+        <v>-0.007608238755779773</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.03887015177065765</v>
+        <v>-0.01811685582177387</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.01361720067453627</v>
+        <v>-0.005484387510007993</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.01177694548481066</v>
+        <v>-0.006593406593406637</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0.0004295197188598499</v>
+        <v>-0.0007973143096937418</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.005705832628909546</v>
+        <v>-0.005659592176446082</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.003483004616030205</v>
+        <v>-0.004283426741393093</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.004395604395604403</v>
+        <v>-0.0008030431107354352</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0.007480980557903627</v>
+        <v>-0.006382079459002554</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.007074490220557661</v>
+        <v>-0.004395604395604435</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0.005367709213863048</v>
+        <v>0.0003372681281618828</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.0004876066639577403</v>
+        <v>-0.0006762468300929969</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.0009721048182586677</v>
+        <v>-0.0006095083299471838</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.002108551347130072</v>
+        <v>-0.00287404902789522</v>
       </c>
       <c r="CA5" t="n">
         <v>0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0.00244195356285023</v>
+        <v>-0.002197802197802223</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.003828547648772373</v>
+        <v>-0.00674522551808211</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0.0001681378730559291</v>
+        <v>-0.001218999579655367</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.0008739076154806402</v>
+        <v>-0.00197562000840692</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.008743169398907114</v>
+        <v>-0.00377675199328581</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.009488139825218501</v>
+        <v>-0.007438715131022844</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.002663337494798179</v>
+        <v>-0.0008453085376162517</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0.005909280066583445</v>
+        <v>-0.006677937447168247</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0.007990012484394526</v>
+        <v>-0.002153596099146704</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0.005874947545111165</v>
+        <v>-0.009777591271506547</v>
       </c>
     </row>
     <row r="6">
@@ -1961,268 +1961,268 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.0006611577357082011</v>
+        <v>-0.00289049745964047</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.002748577651617656</v>
+        <v>-0.002841249279073662</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.000150198744561178</v>
+        <v>-0.002919356217558275</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.004354795379316265</v>
+        <v>-0.001799086824265483</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.002714985385267283</v>
+        <v>-0.001340659081808096</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.00297717341733218</v>
+        <v>0.000694033905441585</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0001838500157641837</v>
+        <v>-6.305170239596369e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.004459547512972372</v>
+        <v>-0.0006114133797165633</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.002136198239802414</v>
+        <v>-0.00594824504028812</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.01498561026097236</v>
+        <v>-0.009028178962037878</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.001474571796525115</v>
+        <v>-0.003667285735238108</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.002195716568454692</v>
+        <v>-0.003580266647224647</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.003376830713416687</v>
+        <v>-0.002476353722508034</v>
       </c>
       <c r="P6" t="n">
-        <v>0.003643106215020847</v>
+        <v>0.008766611698515839</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0009993420152585863</v>
+        <v>-0.001448039618810043</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.001564274664766363</v>
+        <v>-0.003392799169517999</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.002246577429077076</v>
+        <v>-0.003073147682049996</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.005987549961524607</v>
+        <v>-0.005600059541713292</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.003540236382430911</v>
+        <v>-0.003285342638482408</v>
       </c>
       <c r="V6" t="n">
-        <v>1.050861706599349e-05</v>
+        <v>-0.0002263131647720296</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.0005132182920379424</v>
+        <v>0.004272618932139713</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.001874912923295791</v>
+        <v>-0.00330486705509804</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.001688854235973872</v>
+        <v>-0.00169942163330046</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.000504270589250791</v>
+        <v>-0.0005903857966435722</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.0008992147225810849</v>
+        <v>-0.001974561883850745</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.0001260504868713319</v>
+        <v>-0.0003407463916625914</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.009534159483955357</v>
+        <v>-0.006376284459520289</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.008197192882135886</v>
+        <v>-0.005977619304285781</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.0007762355820535056</v>
+        <v>-0.002327686435506154</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.001541176213811646</v>
+        <v>-0.003154812560216144</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.0003380459453746903</v>
+        <v>-0.0001547482516737975</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.0007608850904350761</v>
+        <v>-0.0004103557224616611</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.001867781348436168</v>
+        <v>-0.001908716712108671</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.006932749695386781</v>
+        <v>-0.002251348248410068</v>
       </c>
       <c r="AL6" t="n">
-        <v>9.830908375940694e-06</v>
+        <v>-0.000728076662124233</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.001098300246987757</v>
+        <v>6.32377740303086e-05</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.001175064887983296</v>
+        <v>-0.003753631179441377</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.001726733093067623</v>
+        <v>-0.00204702586179385</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.0007772675480686803</v>
+        <v>-0.0008352676957590675</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.001306459625469872</v>
+        <v>0.0004645855048818565</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.001216751078349301</v>
+        <v>-0.001101829052340392</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.002182511438649512</v>
+        <v>-0.000673789423073537</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0.007783856341062759</v>
+        <v>-0.00514636508468152</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.001212805711605835</v>
+        <v>-0.002779109412705871</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.001305146426719262</v>
+        <v>0.001201044015385513</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.001628148289144271</v>
+        <v>-0.00301899158375318</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.0001169653722664726</v>
+        <v>-6.289308176102569e-05</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.001942825586521707</v>
+        <v>-0.001287894848420618</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.004014246148969177</v>
+        <v>0.0004494713476831169</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.009073844105465984</v>
+        <v>-0.001422120146994011</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.01238243884975523</v>
+        <v>-0.008276476706550679</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.001053422181823641</v>
+        <v>-6.242197253429616e-05</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.000410229729701278</v>
+        <v>-0.0003665784924260257</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.0003621666537307749</v>
+        <v>-0.0003061808637466829</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.008215979725634707</v>
+        <v>-0.007426113645052179</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.0005555995428836779</v>
+        <v>-0.00237309030719621</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0.0009711792919168487</v>
+        <v>-9.485666104554202e-05</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-0.004859465139558278</v>
+        <v>-0.0005219183778726071</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.005209047640966286</v>
+        <v>-0.003345483512388597</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0.001158240211900052</v>
+        <v>-0.0002721440966088201</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.003316383723364841</v>
+        <v>-0.0007748694739940248</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0.01443178502448869</v>
+        <v>-0.005976056817552027</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.005483207380003848</v>
+        <v>-0.001565645879693653</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.003194790518859797</v>
+        <v>-0.0006977800448052546</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-0.0001005542379396179</v>
+        <v>-7.053021872424625e-05</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0.00225681736471432</v>
+        <v>-0.001995232325052551</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.001714968255672533</v>
+        <v>-0.001956791432093552</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0.0003197439349731907</v>
+        <v>-0.0001161305240394067</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0.001099215863306188</v>
+        <v>0.001324233818092485</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.004284551584119925</v>
+        <v>-0.0004636875118543465</v>
       </c>
       <c r="BW6" t="n">
-        <v>-0.0007795390869093393</v>
+        <v>0.001511650213319299</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.0001686030521418885</v>
+        <v>-8.306771520620871e-05</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.0007446502517931442</v>
+        <v>-0.0001585023358239068</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.0005061427416791359</v>
+        <v>-3.080308551912936e-05</v>
       </c>
       <c r="CA6" t="n">
         <v>0</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0.0008283132653403968</v>
+        <v>-0.0002521274992664135</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0.001139135943023956</v>
+        <v>-0.0001480131705095644</v>
       </c>
       <c r="CD6" t="n">
         <v>0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.0003802284756364294</v>
+        <v>0.000260876734270854</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.00284979710708832</v>
+        <v>0.0005566968004440731</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0.0005468522650111718</v>
+        <v>-0.002569431519921559</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.000661819562209931</v>
+        <v>-0.0003041943676866027</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0.00242386813612481</v>
+        <v>-0.002404531249813522</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0.001023337590869514</v>
+        <v>0.0001891843038432012</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0.001067537468129609</v>
+        <v>-0.0007923562568288522</v>
       </c>
     </row>
     <row r="7">
@@ -2232,268 +2232,268 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0009354396612060111</v>
+        <v>-0.0006771943336579655</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0006511377797159712</v>
+        <v>-0.0007763147592441899</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0007814721378780365</v>
+        <v>0.0002913025384935597</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.00164153808146158</v>
+        <v>0.0009507648456380468</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001439758605037811</v>
+        <v>0.001167493860180902</v>
       </c>
       <c r="H7" t="n">
-        <v>0.006450339037531649</v>
+        <v>0.002884582250284612</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.214250320999311e-05</v>
+        <v>-5.551115123125783e-18</v>
       </c>
       <c r="J7" t="n">
-        <v>0.003283848928902078</v>
+        <v>0.002075998195331769</v>
       </c>
       <c r="K7" t="n">
-        <v>0.006543273413794959</v>
+        <v>0.01025509131329442</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01547917652416927</v>
+        <v>0.009291821612029971</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0001481750448521002</v>
+        <v>0.00182138649060794</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0005031622490193121</v>
+        <v>-0.001867145147179716</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0007412140531424193</v>
+        <v>0.002371960079332219</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01093373619160509</v>
+        <v>0.01221235269137741</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.007881021138389043</v>
+        <v>0.004885716753429281</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001005496205001305</v>
+        <v>0.001740094713514895</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0002607662492873807</v>
+        <v>-0.0004931432498443856</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.001967364911652331</v>
+        <v>-0.0006930555445587628</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001074371876855279</v>
+        <v>0.0004420153831835806</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0001224700109650811</v>
+        <v>-2.096436058701134e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>0.004196573265549458</v>
+        <v>0.006094716132658778</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.001232696435372688</v>
+        <v>-0.002339137378425549</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0003629068491547427</v>
+        <v>0.0001265290034909661</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0007994249206038084</v>
+        <v>0.0004620202148758245</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001174620015465955</v>
+        <v>0.0001792473656193117</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0002458638898301946</v>
+        <v>0.000166730527256892</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.0006863088230614992</v>
+        <v>-0.0004441592038324504</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.003897877388977944</v>
+        <v>-0.003305607332041577</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.308504901418204e-05</v>
+        <v>0.0007543773737384741</v>
       </c>
       <c r="AF7" t="n">
-        <v>6.317575015221677e-05</v>
+        <v>0.00284350854582111</v>
       </c>
       <c r="AG7" t="n">
-        <v>6.045634694418212e-05</v>
+        <v>0.0001810226029071771</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.0001688478858020925</v>
+        <v>-0.0002675529352361872</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.002380705945182943</v>
+        <v>0.001387922743944392</v>
       </c>
       <c r="AK7" t="n">
-        <v>-0.001899111071831272</v>
+        <v>0.001606006453505621</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.0002310934181763979</v>
+        <v>-8.322929671243373e-05</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.0002727654217372922</v>
+        <v>0.0003563920739423021</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.0003362340513538454</v>
+        <v>-0.001608563732469304</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.0001688215868540177</v>
+        <v>0.0005038491613479357</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0.0002935727459153937</v>
+        <v>1.746313401440589e-07</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.001635906328105019</v>
+        <v>0.001638277397618337</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.0001201806753941049</v>
+        <v>0.001699538396978567</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.0002618525558783225</v>
+        <v>0.0007120044717279007</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0.002206248693539281</v>
+        <v>-0.001894331243425296</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.0005394664031686646</v>
+        <v>-1.115716920235262e-05</v>
       </c>
       <c r="AV7" t="n">
-        <v>-0.000147592288376025</v>
+        <v>0.002239701958797402</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.001242022080235294</v>
+        <v>-0.0001054497454809011</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.0002944202276029539</v>
+        <v>0.0003498014722555898</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0.00115436167090977</v>
+        <v>0.0004172877549438625</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.0002742730009588468</v>
+        <v>0.003282990610596731</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0.003218713131137435</v>
+        <v>0.000204493959895874</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0.008034194213450812</v>
+        <v>-0.003876687670983259</v>
       </c>
       <c r="BC7" t="n">
-        <v>-0.0003370735231781552</v>
+        <v>0.0002099803115768018</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.0002714621982899456</v>
+        <v>2.112139699590454e-05</v>
       </c>
       <c r="BE7" t="n">
-        <v>-2.101723413198697e-05</v>
+        <v>0.0001435486326943625</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.004128173116937162</v>
+        <v>-0.004004984644023796</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.0009674856459219672</v>
+        <v>0.001238152402904458</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>-2.101723413200363e-05</v>
+        <v>0.0001976161980865032</v>
       </c>
       <c r="BJ7" t="n">
-        <v>-0.001783979844604655</v>
+        <v>0.001160220611670776</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.0004262341273690517</v>
+        <v>7.706282167502265e-06</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.0002098551000499438</v>
+        <v>0.000225182247521416</v>
       </c>
       <c r="BM7" t="n">
-        <v>-0.001310458025524891</v>
+        <v>0.0001677148846960075</v>
       </c>
       <c r="BN7" t="n">
-        <v>-0.004707124191700551</v>
+        <v>-0.002392458745233484</v>
       </c>
       <c r="BO7" t="n">
-        <v>-0.0004628550128086162</v>
+        <v>-0.0003429407463102663</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.0003147297765299539</v>
+        <v>0.0004006207996153311</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0</v>
+        <v>8.203009100483106e-05</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.0005871956406798496</v>
+        <v>0.000843285217827816</v>
       </c>
       <c r="BS7" t="n">
-        <v>6.305170239594981e-05</v>
+        <v>-0.0002103584129542924</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.0001677148846960075</v>
+        <v>0.0004126487773027487</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.000501260217181354</v>
+        <v>0.001818967081438977</v>
       </c>
       <c r="BV7" t="n">
-        <v>-0.0001853442900101089</v>
+        <v>0.001725748137867084</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.0005872318912822861</v>
+        <v>0.002444585546567268</v>
       </c>
       <c r="BX7" t="n">
-        <v>-4.062617733886497e-05</v>
+        <v>-3.932363350372392e-05</v>
       </c>
       <c r="BY7" t="n">
-        <v>-3.695981571664726e-05</v>
+        <v>0.0003450265883405857</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1.966181675188139e-05</v>
+        <v>0.0009476740270721207</v>
       </c>
       <c r="CA7" t="n">
         <v>0</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.0005278901925678759</v>
+        <v>0.0004596646687424932</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.0007366146190529387</v>
+        <v>0.001574425083803937</v>
       </c>
       <c r="CD7" t="n">
         <v>0</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.0003658325945463115</v>
+        <v>0.000718716188390467</v>
       </c>
       <c r="CF7" t="n">
-        <v>-0.001274338202060071</v>
+        <v>0.002280015051770901</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.00219355483027544</v>
+        <v>-0.0007708132130434475</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.0001047689293900145</v>
+        <v>0.0002937499429816248</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.0005504997457187244</v>
+        <v>-0.0008559468119569035</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.002202595076410407</v>
+        <v>0.002506625874055063</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.0008438652409984704</v>
+        <v>0.0006288159201869259</v>
       </c>
     </row>
     <row r="8">
@@ -2503,268 +2503,268 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002158328200855758</v>
+        <v>0.002998133358787497</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0001049941490696815</v>
+        <v>0.002967809852619788</v>
       </c>
       <c r="E8" t="n">
-        <v>0.004699883867318014</v>
+        <v>0.001162055520210012</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0008880790230572587</v>
+        <v>0.003083319255241382</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001395896638635674</v>
+        <v>0.003388408453936667</v>
       </c>
       <c r="H8" t="n">
-        <v>0.009484934554714053</v>
+        <v>0.003770526622928058</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0003368559724520631</v>
+        <v>0.0001478755386525227</v>
       </c>
       <c r="J8" t="n">
-        <v>0.004070627592522047</v>
+        <v>0.00524836887987277</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02033970902812734</v>
+        <v>0.02250202620773063</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02846094867777008</v>
+        <v>0.02540677175508638</v>
       </c>
       <c r="M8" t="n">
-        <v>0.001815290576858194</v>
+        <v>0.002843552119477913</v>
       </c>
       <c r="N8" t="n">
-        <v>0.003415512574057708</v>
+        <v>-0.001168175358214818</v>
       </c>
       <c r="O8" t="n">
-        <v>0.002371077156998783</v>
+        <v>0.008016063623207169</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01470980325575806</v>
+        <v>0.02167167852221467</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01320775128204737</v>
+        <v>0.01097725376100889</v>
       </c>
       <c r="R8" t="n">
-        <v>0.004417642313343495</v>
+        <v>0.004389293345073325</v>
       </c>
       <c r="S8" t="n">
-        <v>0.002607280640662352</v>
+        <v>0.000756620428751542</v>
       </c>
       <c r="T8" t="n">
-        <v>0.001761258818588282</v>
+        <v>0.004023376416034308</v>
       </c>
       <c r="U8" t="n">
-        <v>0.003790464494383211</v>
+        <v>0.001852446961581827</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0001533745992668173</v>
+        <v>4.153385760310435e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>0.008752361429146547</v>
+        <v>0.01637118145034844</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001668869624343755</v>
+        <v>0.001605967939656258</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.001318608600154181</v>
+        <v>0.001059070324458466</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.001227756779342631</v>
+        <v>0.002458582248479815</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.002832369388834158</v>
+        <v>0.001355266337859479</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0006013113771675321</v>
+        <v>0.0007401373694957664</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.003099210418684925</v>
+        <v>0.0024560564255381</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0.001965676038246697</v>
+        <v>0.001486645904616465</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.0008789503507628221</v>
+        <v>0.003399461141947305</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.00736180884060433</v>
+        <v>0.009094636564883688</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0005811337828510483</v>
+        <v>0.0005687021050597652</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0005769685868894952</v>
+        <v>0.0004090021788681314</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.006509635549572238</v>
+        <v>0.005806572431772817</v>
       </c>
       <c r="AK8" t="n">
-        <v>-0.001016243875776884</v>
+        <v>0.004497891720371738</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.001012246420630161</v>
+        <v>0.0008510837205223387</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.0002735127419868894</v>
+        <v>0.001200064227247702</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.001585786915021659</v>
+        <v>-0.0004756023594597314</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.001288721331852746</v>
+        <v>0.004837333343786806</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.0005225428234662321</v>
+        <v>0.0005289011083080108</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.003367137257481789</v>
+        <v>0.003102887159983839</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.003446578877041723</v>
+        <v>0.004668430980182811</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.001907970752393151</v>
+        <v>0.00140631082436227</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.003261468816621221</v>
+        <v>0.007794455123613337</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.001792532140506164</v>
+        <v>0.002853834139190276</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.001144765989339738</v>
+        <v>0.003907932778570941</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.004155528189108817</v>
+        <v>0.002101053119537838</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.000587688786886667</v>
+        <v>0.00137293036444035</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0.0007091795358097814</v>
+        <v>0.001819463136713656</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.001293339466830898</v>
+        <v>0.00638316394365987</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.0008029589343087285</v>
+        <v>0.001320878376205967</v>
       </c>
       <c r="BB8" t="n">
-        <v>-0.001497702999236991</v>
+        <v>-0.0009442948167823651</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.000208655420927456</v>
+        <v>0.0009322960125226626</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.0006479724974825657</v>
+        <v>0.0005779033814021755</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.0007552448290696401</v>
+        <v>0.0009543013950684464</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.003159070579440248</v>
+        <v>0.0003122980531774344</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.004706789418951654</v>
+        <v>0.002726012294782388</v>
       </c>
       <c r="BH8" t="n">
         <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.0005098579605681442</v>
+        <v>0.0004219681159463279</v>
       </c>
       <c r="BJ8" t="n">
-        <v>-0.001129744882177095</v>
+        <v>0.003731277338217381</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.003770287141073655</v>
+        <v>0.004339123964991592</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.0007291172989776551</v>
+        <v>0.0007563624047496109</v>
       </c>
       <c r="BM8" t="n">
-        <v>-0.0002533520118485594</v>
+        <v>0.002373523858239268</v>
       </c>
       <c r="BN8" t="n">
-        <v>-0.0007938190469460205</v>
+        <v>0.002822045401614709</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.001262349299570659</v>
+        <v>0.001901795321219982</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.004929622030302224</v>
+        <v>0.007346711084866819</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.000168195612710112</v>
+        <v>0.0004618543760190274</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.007247056423034125</v>
+        <v>0.009736831078986782</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.001243974901103009</v>
+        <v>0.002776276578312556</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.001335344575160863</v>
+        <v>0.00206399845397651</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.003108617387316712</v>
+        <v>0.01174310192163818</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.006047728207841038</v>
+        <v>0.003373075015301732</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.01000361667125416</v>
+        <v>0.009953612322392566</v>
       </c>
       <c r="BX8" t="n">
-        <v>5.857087075361589e-05</v>
+        <v>0.000274108547396329</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.001103034366485175</v>
+        <v>0.0006477709640239471</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.0003645647514673028</v>
+        <v>0.00169770176011336</v>
       </c>
       <c r="CA8" t="n">
         <v>0</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.001127869419625296</v>
+        <v>0.0009712408749795288</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.002442319611819352</v>
+        <v>0.00646765544563061</v>
       </c>
       <c r="CD8" t="n">
         <v>0</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.0005525475640725474</v>
+        <v>0.002038038319871163</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.000412649194105949</v>
+        <v>0.004863051497433055</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.003141385538054098</v>
+        <v>0.002123380766136884</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.001810535584663331</v>
+        <v>0.001535255530914611</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.002985718736243978</v>
+        <v>0.001604058590224525</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.01181296248452636</v>
+        <v>0.00370858332773652</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.003037341583527533</v>
+        <v>0.004226704284161459</v>
       </c>
     </row>
     <row r="9">
@@ -2774,268 +2774,268 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003699033207229907</v>
+        <v>0.0157360406091371</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02017654476670868</v>
+        <v>0.03417402269861284</v>
       </c>
       <c r="E9" t="n">
-        <v>0.009605622803592317</v>
+        <v>0.01155798516204611</v>
       </c>
       <c r="F9" t="n">
-        <v>0.003642914331465219</v>
+        <v>0.003735745182854922</v>
       </c>
       <c r="G9" t="n">
-        <v>0.005548549810844882</v>
+        <v>0.01071878940731399</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01151893791487695</v>
+        <v>0.01198699715562778</v>
       </c>
       <c r="I9" t="n">
-        <v>0.000676246830093008</v>
+        <v>0.0009761811792269204</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01690369768386831</v>
+        <v>0.007458024209293301</v>
       </c>
       <c r="K9" t="n">
-        <v>0.06407964242177973</v>
+        <v>0.05522145469321414</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05574969524583501</v>
+        <v>0.05713124746038193</v>
       </c>
       <c r="M9" t="n">
-        <v>0.003499803381832534</v>
+        <v>0.00991800078094498</v>
       </c>
       <c r="N9" t="n">
-        <v>0.005590584279108857</v>
+        <v>0.01226083561108947</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01144084342053884</v>
+        <v>0.01846934791097232</v>
       </c>
       <c r="P9" t="n">
-        <v>0.05298711440843418</v>
+        <v>0.05393258426966296</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.02709878953533773</v>
+        <v>0.01399662731871837</v>
       </c>
       <c r="R9" t="n">
-        <v>0.01422186103210075</v>
+        <v>0.01105037094884815</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01354939476766885</v>
+        <v>0.007145646231940694</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01034211561148254</v>
+        <v>0.009019914096056269</v>
       </c>
       <c r="U9" t="n">
-        <v>0.007608238755779739</v>
+        <v>0.0201874267864116</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0005494505494505808</v>
+        <v>0.00158472165786262</v>
       </c>
       <c r="W9" t="n">
-        <v>0.02559300873907615</v>
+        <v>0.02808988764044946</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01249511909410383</v>
+        <v>0.01206389239176122</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.009305160503860188</v>
+        <v>0.008015107007973098</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.002401921537229834</v>
+        <v>0.007650273224043691</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.01141812271434374</v>
+        <v>0.009955302722470537</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.001160928742994471</v>
+        <v>0.001636592530423775</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.01622971285892635</v>
+        <v>0.009696213066999604</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.001081980857261744</v>
+        <v>0.01754015215553674</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.01038656774697381</v>
+        <v>0.02206169465052716</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.01960171807887541</v>
+        <v>0.01424344885883344</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0009651699538397174</v>
+        <v>0.001259650548557467</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.001178382771231179</v>
+        <v>0.001952362358453741</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.01003514252245213</v>
+        <v>0.01569699336196804</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.009488481062085075</v>
+        <v>0.009121479613282867</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.001381552214546899</v>
+        <v>0.001625355546525764</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.0009643605870021</v>
+        <v>0.002059688944934823</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.0092238927265339</v>
+        <v>0.002348008385744205</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.006559937524404491</v>
+        <v>0.01569699336196804</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.001909792767167773</v>
+        <v>0.004295197188598254</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.008911307271962998</v>
+        <v>0.007192198293376639</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.012573213588442</v>
+        <v>0.0151112846544319</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.003460479748328782</v>
+        <v>0.003068516183270253</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.009630231613165363</v>
+        <v>0.02356765542462411</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.01187036313939863</v>
+        <v>0.01128465443186261</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.01544087769199509</v>
+        <v>0.008533116619260438</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.01381552214546931</v>
+        <v>0.0206826493295408</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.002275497765136092</v>
+        <v>0.002762209767814294</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.02149532710280373</v>
+        <v>0.004754164973587949</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.01576594880130027</v>
+        <v>0.01635140815468682</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.0100365704997968</v>
+        <v>0.00605232331120662</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.002789518174133554</v>
+        <v>0.009541824295922619</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.001259650548557478</v>
+        <v>0.001216953420058709</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.002096436058700235</v>
+        <v>0.002459976571651734</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.001180438448566634</v>
+        <v>0.001730239874164441</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.0119484576337368</v>
+        <v>0.005505661850839572</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.02775294595692806</v>
+        <v>0.02060138155221453</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.001061738104600929</v>
+        <v>0.003441040704993659</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.01901665989435185</v>
+        <v>0.02401462819991872</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.02312068264932953</v>
+        <v>0.01466771529689346</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.001337003539127091</v>
+        <v>0.001340918325883755</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.009548963835839053</v>
+        <v>0.01556277935798453</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.005348014156508108</v>
+        <v>0.01905729378301502</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.004307192198293353</v>
+        <v>0.01597032409215154</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.01147989066770788</v>
+        <v>0.01348800629178141</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.001219032638615858</v>
+        <v>0.001179709005112128</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.008827238335435039</v>
+        <v>0.0128465443186256</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.009567654123298663</v>
+        <v>0.007926591175322217</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.002831301612269022</v>
+        <v>0.008808493904836835</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.01725888324873094</v>
+        <v>0.02327215931276848</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.01160928742994399</v>
+        <v>0.01308082780164002</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.01837469975980787</v>
+        <v>0.01993708218639405</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.0002113271344040824</v>
+        <v>0.0007973143096936086</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.002988596146283973</v>
+        <v>0.004168305151396046</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.00142557651991615</v>
+        <v>0.00334250884781756</v>
       </c>
       <c r="CA9" t="n">
         <v>0</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.007356031946195885</v>
+        <v>0.002595359811246589</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.003242594075260252</v>
+        <v>0.01408154686843209</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.000419639110365122</v>
+        <v>0.0002098195551825222</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.00380304243394719</v>
+        <v>0.003709488481062129</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.007692307692307676</v>
+        <v>0.00925419757907071</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.006845476381104931</v>
+        <v>0.006565252201761429</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.00263468344475033</v>
+        <v>0.003572929802437985</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.01073799297149548</v>
+        <v>0.009566575556423308</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.01526747364310813</v>
+        <v>0.02955876610698951</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.01426249492076389</v>
+        <v>0.01134930643127362</v>
       </c>
     </row>
   </sheetData>
